--- a/DJM01N.xlsx
+++ b/DJM01N.xlsx
@@ -11,671 +11,671 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1248" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1254" uniqueCount="437">
   <si>
     <t/>
   </si>
   <si>
+    <t>20130374</t>
+  </si>
+  <si>
+    <t>BENTOEL SJT 12''S</t>
+  </si>
+  <si>
+    <t>DJM01N</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20055060</t>
+  </si>
+  <si>
+    <t>DUNHILL FC FTLR 16'S</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>20100889</t>
+  </si>
+  <si>
+    <t>DUNHILL FC FTLR 12'S</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20002901</t>
+  </si>
+  <si>
+    <t>DUNHILL HIJAU MNTH20</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20007397</t>
+  </si>
+  <si>
+    <t>DUNHILL BIRU LGHT 20</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20096704</t>
+  </si>
+  <si>
+    <t>DUNHILL MILD BKS 16S</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20039178</t>
+  </si>
+  <si>
+    <t>DUNHILL F/C MILD20'S</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20137296</t>
+  </si>
+  <si>
+    <t>DUNHILL EVOQUE 16S</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20141502</t>
+  </si>
+  <si>
+    <t>DUNHILL MIXTURES 12S</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20137298</t>
+  </si>
+  <si>
+    <t>L.STRIKE BRY FRZ 20S</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>20102468</t>
+  </si>
+  <si>
+    <t>LUCKY/S PRPLE BOST20</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>10010112</t>
+  </si>
+  <si>
+    <t>LUCKY STRIKE FILTR20</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>10010113</t>
+  </si>
+  <si>
+    <t>LUCKY.ST CL.SWITC 20</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>20098080</t>
+  </si>
+  <si>
+    <t>ASPRO FLTR BOLD20'S</t>
+  </si>
+  <si>
+    <t>20137571</t>
+  </si>
+  <si>
+    <t>TWIZZ PRIME 16'S</t>
+  </si>
+  <si>
+    <t>20123283</t>
+  </si>
+  <si>
+    <t>TWIZZ R/F RYL CR 16S</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20123284</t>
+  </si>
+  <si>
+    <t>TWIZZ YELLOW CR 16'S</t>
+  </si>
+  <si>
+    <t>20129762</t>
+  </si>
+  <si>
+    <t>TWIZZ R/F RYL CR 12S</t>
+  </si>
+  <si>
+    <t>20139762</t>
+  </si>
+  <si>
+    <t>TWIZZ PRM ROYAL 16S</t>
+  </si>
+  <si>
+    <t>20139763</t>
+  </si>
+  <si>
+    <t>TWIZZ PRM TRPCL 16S</t>
+  </si>
+  <si>
+    <t>20113074</t>
+  </si>
+  <si>
+    <t>MARLBORO KRETEK 12'S</t>
+  </si>
+  <si>
+    <t>20122038</t>
+  </si>
+  <si>
+    <t>MRLBORO KRT BIRU 12S</t>
+  </si>
+  <si>
+    <t>20126739</t>
+  </si>
+  <si>
+    <t>DUFF FILTER BOLD20'S</t>
+  </si>
+  <si>
+    <t>20130572</t>
+  </si>
+  <si>
+    <t>BHUMI KRETEK 12S</t>
+  </si>
+  <si>
+    <t>20138842</t>
+  </si>
+  <si>
+    <t>DUFF FILTER RED 20'S</t>
+  </si>
+  <si>
+    <t>20117725</t>
+  </si>
+  <si>
+    <t>NESLITE MAX 20'S</t>
+  </si>
+  <si>
+    <t>TG</t>
+  </si>
+  <si>
+    <t>20124230</t>
+  </si>
+  <si>
+    <t>MAGNUM MAX FILTER20S</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>10010094</t>
+  </si>
+  <si>
+    <t>SAMPOERNA KRT12S/PCS</t>
+  </si>
+  <si>
+    <t>20107794</t>
+  </si>
+  <si>
+    <t>DJI SAM SOE EDS 12'S</t>
+  </si>
+  <si>
+    <t>10010088</t>
+  </si>
+  <si>
+    <t>234  KRT 12/PCS</t>
+  </si>
+  <si>
+    <t>20004283</t>
+  </si>
+  <si>
+    <t>DJI SAM SOE MGNUM 12</t>
+  </si>
+  <si>
+    <t>20135213</t>
+  </si>
+  <si>
+    <t>DJI SAM SOE KRT MGM</t>
+  </si>
+  <si>
+    <t>20138213</t>
+  </si>
+  <si>
+    <t>MAGNUM KRT CKLT 12'S</t>
+  </si>
+  <si>
+    <t>20134964</t>
+  </si>
+  <si>
+    <t>SMPOERNA LGT NIRA12S</t>
+  </si>
+  <si>
+    <t>20134790</t>
+  </si>
+  <si>
+    <t>SAMPOERNA PRIMA 12'S</t>
+  </si>
+  <si>
+    <t>20138480</t>
+  </si>
+  <si>
+    <t>SMPOERNA LG NSKA 12S</t>
+  </si>
+  <si>
+    <t>20139347</t>
+  </si>
+  <si>
+    <t>MAGNUM VNTR GLD 12S</t>
+  </si>
+  <si>
+    <t>20139534</t>
+  </si>
+  <si>
+    <t>DJI SAM SOE S/P 12S</t>
+  </si>
+  <si>
+    <t>20132342</t>
+  </si>
+  <si>
+    <t>DJI SAM SOE MAESTR12</t>
+  </si>
+  <si>
+    <t>10010100</t>
+  </si>
+  <si>
+    <t>MARLBORO HPACK 20'S</t>
+  </si>
+  <si>
+    <t>20107181</t>
+  </si>
+  <si>
+    <t>MARLBORO SE 20'S</t>
+  </si>
+  <si>
+    <t>10010102</t>
+  </si>
+  <si>
+    <t>MARLBORO LIGHT 20'S</t>
+  </si>
+  <si>
+    <t>20107184</t>
+  </si>
+  <si>
+    <t>MARLBORO GOLD SE 20S</t>
+  </si>
+  <si>
+    <t>20043389</t>
+  </si>
+  <si>
+    <t>MARLBORO BLS/BRST 20</t>
+  </si>
+  <si>
+    <t>20107180</t>
+  </si>
+  <si>
+    <t>MRLBORO ICE BR SE20S</t>
+  </si>
+  <si>
+    <t>20135544</t>
+  </si>
+  <si>
+    <t>MARLBORO TRPCL BS16S</t>
+  </si>
+  <si>
+    <t>20070618</t>
+  </si>
+  <si>
+    <t>MARLBORO BLACK 20'S</t>
+  </si>
+  <si>
+    <t>20083490</t>
+  </si>
+  <si>
+    <t>MARLBORO BLACK 12'S</t>
+  </si>
+  <si>
+    <t>20105344</t>
+  </si>
+  <si>
+    <t>MARLBORO BLACK 16'S</t>
+  </si>
+  <si>
+    <t>20125676</t>
+  </si>
+  <si>
+    <t>DJI SAM SOE MG BIN12</t>
+  </si>
+  <si>
+    <t>20136297</t>
+  </si>
+  <si>
+    <t>DJI SAM SOE TIN 12S</t>
+  </si>
+  <si>
+    <t>10030733</t>
+  </si>
+  <si>
+    <t>DJI SAM SOE S/PRM</t>
+  </si>
+  <si>
+    <t>20134530</t>
+  </si>
+  <si>
+    <t>DJI SAM SOE SP.PRM16</t>
+  </si>
+  <si>
+    <t>10010090</t>
+  </si>
+  <si>
+    <t>SAMPOERNA MLD 12/MRH</t>
+  </si>
+  <si>
+    <t>10010091</t>
+  </si>
+  <si>
+    <t>SAMPOERNA MILD 16'S</t>
+  </si>
+  <si>
+    <t>20135439</t>
+  </si>
+  <si>
+    <t>SAMPOERNA 35TH ED16S</t>
+  </si>
+  <si>
+    <t>20131370</t>
+  </si>
+  <si>
+    <t>SAMPOERNA ROYAL 16'S</t>
+  </si>
+  <si>
+    <t>20079512</t>
+  </si>
+  <si>
+    <t>SMPOERNA MNTHL.BR 16</t>
+  </si>
+  <si>
+    <t>20095217</t>
+  </si>
+  <si>
+    <t>SMPOERNA TRPCAL 16'S</t>
+  </si>
+  <si>
+    <t>20064088</t>
+  </si>
+  <si>
+    <t>SMPOERNA AVOLTN 20'S</t>
+  </si>
+  <si>
+    <t>20064089</t>
+  </si>
+  <si>
+    <t>SMPOERNA AVLT MNT 20</t>
+  </si>
+  <si>
+    <t>20136036</t>
+  </si>
+  <si>
+    <t>SMPOERN AVL TW/BRZ20</t>
+  </si>
+  <si>
+    <t>20138598</t>
+  </si>
+  <si>
+    <t>SMPOERN AVL RY.BRS20</t>
+  </si>
+  <si>
+    <t>20139332</t>
+  </si>
+  <si>
+    <t>MRLBORO SUMMER/B 16S</t>
+  </si>
+  <si>
+    <t>20136035</t>
+  </si>
+  <si>
+    <t>MARLBORO PRPLE BS16S</t>
+  </si>
+  <si>
+    <t>20138112</t>
+  </si>
+  <si>
+    <t>MRLBORO RED TITA.20</t>
+  </si>
+  <si>
+    <t>20138113</t>
+  </si>
+  <si>
+    <t>MRLBORO GOLD TITA.20</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>20033460</t>
+  </si>
+  <si>
+    <t>DJARUM COKLT EXTR12S</t>
+  </si>
+  <si>
+    <t>10010083</t>
+  </si>
+  <si>
+    <t>DJARUM KRT CKT12/PCS</t>
+  </si>
+  <si>
+    <t>20135180</t>
+  </si>
+  <si>
+    <t>DJARUM76 FILT.NNS12S</t>
+  </si>
+  <si>
+    <t>20136122</t>
+  </si>
+  <si>
+    <t>DJRM CKLT EXT MOC 12</t>
+  </si>
+  <si>
+    <t>20130634</t>
+  </si>
+  <si>
+    <t>DJARUM 76 MANGGA 12S</t>
+  </si>
+  <si>
+    <t>20138087</t>
+  </si>
+  <si>
+    <t>DJARUM CKLT ELITE 12</t>
+  </si>
+  <si>
+    <t>20138754</t>
+  </si>
+  <si>
+    <t>DJARUM76 FILT.APL12S</t>
+  </si>
+  <si>
+    <t>20139003</t>
+  </si>
+  <si>
+    <t>DJARUM76 MGA RYL12'S</t>
+  </si>
+  <si>
+    <t>20084820</t>
+  </si>
+  <si>
+    <t>FORTE ORGL BKS 20'S</t>
+  </si>
+  <si>
+    <t>20084821</t>
+  </si>
+  <si>
+    <t>FORTE MNTHL BKS 20'S</t>
+  </si>
+  <si>
+    <t>20132549</t>
+  </si>
+  <si>
+    <t>FORTE MANGO BKS 20'S</t>
+  </si>
+  <si>
+    <t>10014528</t>
+  </si>
+  <si>
+    <t>DJARUM BLACK FILTR16</t>
+  </si>
+  <si>
+    <t>10035030</t>
+  </si>
+  <si>
+    <t>DJRM BLACK CPCINO 16</t>
+  </si>
+  <si>
+    <t>20131992</t>
+  </si>
+  <si>
+    <t>DJARUM MILD F.COLA16</t>
+  </si>
+  <si>
+    <t>20046279</t>
+  </si>
+  <si>
+    <t>DJARUM SPR MILD 20'S</t>
+  </si>
+  <si>
+    <t>20075616</t>
+  </si>
+  <si>
+    <t>DJARUM MILD BLCK 12S</t>
+  </si>
+  <si>
+    <t>10010087</t>
+  </si>
+  <si>
+    <t>MR.BROWN COFFEE 12'S</t>
+  </si>
+  <si>
+    <t>20136123</t>
+  </si>
+  <si>
+    <t>DJARUM ESPRSO GLD12S</t>
+  </si>
+  <si>
+    <t>20132548</t>
+  </si>
+  <si>
+    <t>DJARUM ESPRESSO 12'S</t>
+  </si>
+  <si>
+    <t>20140378</t>
+  </si>
+  <si>
+    <t>DJARUM SUPER WRAP12S</t>
+  </si>
+  <si>
+    <t>20139142</t>
+  </si>
+  <si>
+    <t>DJRM CGRILLOS FC 12S</t>
+  </si>
+  <si>
+    <t>10010081</t>
+  </si>
+  <si>
+    <t>DJARUM SUPER FILTR12</t>
+  </si>
+  <si>
+    <t>10010082</t>
+  </si>
+  <si>
+    <t>DJARUM SUPER FILTR16</t>
+  </si>
+  <si>
+    <t>20126488</t>
+  </si>
+  <si>
+    <t>DJARUM KING FLTER 12</t>
+  </si>
+  <si>
+    <t>20075632</t>
+  </si>
+  <si>
+    <t>LA BOLD BKS 12'S</t>
+  </si>
+  <si>
+    <t>20062125</t>
+  </si>
+  <si>
+    <t>LA BOLD BKS 20'S</t>
+  </si>
+  <si>
+    <t>20134688</t>
+  </si>
+  <si>
+    <t>LA BOLD BKS NEW 16'S</t>
+  </si>
+  <si>
+    <t>20124037</t>
+  </si>
+  <si>
+    <t>LA ICE FL PR/BST 16S</t>
+  </si>
+  <si>
+    <t>20135993</t>
+  </si>
+  <si>
+    <t>LA ICE MANGO BST 16S</t>
+  </si>
+  <si>
+    <t>20048746</t>
+  </si>
+  <si>
+    <t>LA ICE 16'S BKS</t>
+  </si>
+  <si>
+    <t>10010084</t>
+  </si>
+  <si>
+    <t>LA FILTER LIGHT 16'S</t>
+  </si>
+  <si>
     <t>20136196</t>
   </si>
   <si>
     <t>CLAS MILD PURPLE 16S</t>
   </si>
   <si>
-    <t>DJM01N</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>RT</t>
-  </si>
-  <si>
     <t>10024523</t>
   </si>
   <si>
     <t>CLAS MILD FILTER 16S</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20130374</t>
-  </si>
-  <si>
-    <t>BENTOEL SJT 12''S</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20055060</t>
-  </si>
-  <si>
-    <t>DUNHILL FC FTLR 16'S</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20100889</t>
-  </si>
-  <si>
-    <t>DUNHILL FC FTLR 12'S</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20002901</t>
-  </si>
-  <si>
-    <t>DUNHILL HIJAU MNTH20</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20007397</t>
-  </si>
-  <si>
-    <t>DUNHILL BIRU LGHT 20</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20096704</t>
-  </si>
-  <si>
-    <t>DUNHILL MILD BKS 16S</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20039178</t>
-  </si>
-  <si>
-    <t>DUNHILL F/C MILD20'S</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>20137296</t>
-  </si>
-  <si>
-    <t>DUNHILL EVOQUE 16S</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20141502</t>
-  </si>
-  <si>
-    <t>DUNHILL MIXTURES 12S</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20137298</t>
-  </si>
-  <si>
-    <t>L.STRIKE BRY FRZ 20S</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>20102468</t>
-  </si>
-  <si>
-    <t>LUCKY/S PRPLE BOST20</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>10010112</t>
-  </si>
-  <si>
-    <t>LUCKY STRIKE FILTR20</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>10010113</t>
-  </si>
-  <si>
-    <t>LUCKY.ST CL.SWITC 20</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>20098080</t>
-  </si>
-  <si>
-    <t>ASPRO FLTR BOLD20'S</t>
-  </si>
-  <si>
-    <t>20137571</t>
-  </si>
-  <si>
-    <t>TWIZZ PRIME 16'S</t>
-  </si>
-  <si>
-    <t>20123283</t>
-  </si>
-  <si>
-    <t>TWIZZ R/F RYL CR 16S</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20123284</t>
-  </si>
-  <si>
-    <t>TWIZZ YELLOW CR 16'S</t>
-  </si>
-  <si>
-    <t>20129762</t>
-  </si>
-  <si>
-    <t>TWIZZ R/F RYL CR 12S</t>
-  </si>
-  <si>
-    <t>20139762</t>
-  </si>
-  <si>
-    <t>TWIZZ PRM ROYAL 16S</t>
-  </si>
-  <si>
-    <t>20139763</t>
-  </si>
-  <si>
-    <t>TWIZZ PRM TRPCL 16S</t>
-  </si>
-  <si>
-    <t>20113074</t>
-  </si>
-  <si>
-    <t>MARLBORO KRETEK 12'S</t>
-  </si>
-  <si>
-    <t>20122038</t>
-  </si>
-  <si>
-    <t>MRLBORO KRT BIRU 12S</t>
-  </si>
-  <si>
-    <t>20126739</t>
-  </si>
-  <si>
-    <t>DUFF FILTER BOLD20'S</t>
-  </si>
-  <si>
-    <t>20130572</t>
-  </si>
-  <si>
-    <t>BHUMI KRETEK 12S</t>
-  </si>
-  <si>
-    <t>20138842</t>
-  </si>
-  <si>
-    <t>DUFF FILTER RED 20'S</t>
-  </si>
-  <si>
-    <t>20117725</t>
-  </si>
-  <si>
-    <t>NESLITE MAX 20'S</t>
-  </si>
-  <si>
-    <t>TG</t>
-  </si>
-  <si>
-    <t>20124230</t>
-  </si>
-  <si>
-    <t>MAGNUM MAX FILTER20S</t>
-  </si>
-  <si>
-    <t>10010094</t>
-  </si>
-  <si>
-    <t>SAMPOERNA KRT12S/PCS</t>
-  </si>
-  <si>
-    <t>20107794</t>
-  </si>
-  <si>
-    <t>DJI SAM SOE EDS 12'S</t>
-  </si>
-  <si>
-    <t>10010088</t>
-  </si>
-  <si>
-    <t>234  KRT 12/PCS</t>
-  </si>
-  <si>
-    <t>20004283</t>
-  </si>
-  <si>
-    <t>DJI SAM SOE MGNUM 12</t>
-  </si>
-  <si>
-    <t>20134530</t>
-  </si>
-  <si>
-    <t>DJI SAM SOE SP.PRM16</t>
-  </si>
-  <si>
-    <t>20135213</t>
-  </si>
-  <si>
-    <t>DJI SAM SOE KRT MGM</t>
-  </si>
-  <si>
-    <t>20138213</t>
-  </si>
-  <si>
-    <t>MAGNUM KRT CKLT 12'S</t>
-  </si>
-  <si>
-    <t>20134964</t>
-  </si>
-  <si>
-    <t>SMPOERNA LGT NIRA12S</t>
-  </si>
-  <si>
-    <t>20134790</t>
-  </si>
-  <si>
-    <t>SAMPOERNA PRIMA 12'S</t>
-  </si>
-  <si>
-    <t>20138480</t>
-  </si>
-  <si>
-    <t>SMPOERNA LG NSKA 12S</t>
-  </si>
-  <si>
-    <t>20139347</t>
-  </si>
-  <si>
-    <t>MAGNUM VNTR GLD 12S</t>
-  </si>
-  <si>
-    <t>10030733</t>
-  </si>
-  <si>
-    <t>DJI SAM SOE S/PRM</t>
-  </si>
-  <si>
-    <t>20139534</t>
-  </si>
-  <si>
-    <t>DJI SAM SOE S/P 12S</t>
-  </si>
-  <si>
-    <t>20132342</t>
-  </si>
-  <si>
-    <t>DJI SAM SOE MAESTR12</t>
-  </si>
-  <si>
-    <t>10010100</t>
-  </si>
-  <si>
-    <t>MARLBORO HPACK 20'S</t>
-  </si>
-  <si>
-    <t>20107181</t>
-  </si>
-  <si>
-    <t>MARLBORO SE 20'S</t>
-  </si>
-  <si>
-    <t>10010102</t>
-  </si>
-  <si>
-    <t>MARLBORO LIGHT 20'S</t>
-  </si>
-  <si>
-    <t>20107184</t>
-  </si>
-  <si>
-    <t>MARLBORO GOLD SE 20S</t>
-  </si>
-  <si>
-    <t>20043389</t>
-  </si>
-  <si>
-    <t>MARLBORO BLS/BRST 20</t>
-  </si>
-  <si>
-    <t>20107180</t>
-  </si>
-  <si>
-    <t>MRLBORO ICE BR SE20S</t>
-  </si>
-  <si>
-    <t>20135544</t>
-  </si>
-  <si>
-    <t>MARLBORO TRPCL BS16S</t>
-  </si>
-  <si>
-    <t>20136035</t>
-  </si>
-  <si>
-    <t>MARLBORO PRPLE BS16S</t>
-  </si>
-  <si>
-    <t>20139332</t>
-  </si>
-  <si>
-    <t>MRLBORO SUMMER/B 16S</t>
-  </si>
-  <si>
-    <t>20070618</t>
-  </si>
-  <si>
-    <t>MARLBORO BLACK 20'S</t>
-  </si>
-  <si>
-    <t>20083490</t>
-  </si>
-  <si>
-    <t>MARLBORO BLACK 12'S</t>
-  </si>
-  <si>
-    <t>20105344</t>
-  </si>
-  <si>
-    <t>MARLBORO BLACK 16'S</t>
-  </si>
-  <si>
-    <t>20125676</t>
-  </si>
-  <si>
-    <t>DJI SAM SOE MG BIN12</t>
-  </si>
-  <si>
-    <t>20136297</t>
-  </si>
-  <si>
-    <t>DJI SAM SOE TIN 12S</t>
-  </si>
-  <si>
-    <t>10010090</t>
-  </si>
-  <si>
-    <t>SAMPOERNA MLD 12/MRH</t>
-  </si>
-  <si>
-    <t>10010091</t>
-  </si>
-  <si>
-    <t>SAMPOERNA MILD 16'S</t>
-  </si>
-  <si>
-    <t>20135439</t>
-  </si>
-  <si>
-    <t>SAMPOERNA 35TH ED16S</t>
-  </si>
-  <si>
-    <t>20131370</t>
-  </si>
-  <si>
-    <t>SAMPOERNA ROYAL 16'S</t>
-  </si>
-  <si>
-    <t>20079512</t>
-  </si>
-  <si>
-    <t>SMPOERNA MNTHL.BR 16</t>
-  </si>
-  <si>
-    <t>20095217</t>
-  </si>
-  <si>
-    <t>SMPOERNA TRPCAL 16'S</t>
-  </si>
-  <si>
-    <t>20064088</t>
-  </si>
-  <si>
-    <t>SMPOERNA AVOLTN 20'S</t>
-  </si>
-  <si>
-    <t>20064089</t>
-  </si>
-  <si>
-    <t>SMPOERNA AVLT MNT 20</t>
-  </si>
-  <si>
-    <t>20136036</t>
-  </si>
-  <si>
-    <t>SMPOERN AVL TW/BRZ20</t>
-  </si>
-  <si>
-    <t>20138598</t>
-  </si>
-  <si>
-    <t>SMPOERN AVL RY.BRS20</t>
-  </si>
-  <si>
-    <t>20138112</t>
-  </si>
-  <si>
-    <t>MRLBORO RED TITA.20</t>
-  </si>
-  <si>
-    <t>20138113</t>
-  </si>
-  <si>
-    <t>MRLBORO GOLD TITA.20</t>
-  </si>
-  <si>
-    <t>20033460</t>
-  </si>
-  <si>
-    <t>DJARUM COKLT EXTR12S</t>
-  </si>
-  <si>
-    <t>10010083</t>
-  </si>
-  <si>
-    <t>DJARUM KRT CKT12/PCS</t>
-  </si>
-  <si>
-    <t>20135180</t>
-  </si>
-  <si>
-    <t>DJARUM76 FILT.NNS12S</t>
-  </si>
-  <si>
-    <t>20136122</t>
-  </si>
-  <si>
-    <t>DJRM CKLT EXT MOC 12</t>
-  </si>
-  <si>
-    <t>20130634</t>
-  </si>
-  <si>
-    <t>DJARUM 76 MANGGA 12S</t>
-  </si>
-  <si>
-    <t>20138087</t>
-  </si>
-  <si>
-    <t>DJARUM CKLT ELITE 12</t>
-  </si>
-  <si>
-    <t>20138754</t>
-  </si>
-  <si>
-    <t>DJARUM76 FILT.APL12S</t>
-  </si>
-  <si>
-    <t>20139003</t>
-  </si>
-  <si>
-    <t>DJARUM76 MGA RYL12'S</t>
-  </si>
-  <si>
-    <t>20084820</t>
-  </si>
-  <si>
-    <t>FORTE ORGL BKS 20'S</t>
-  </si>
-  <si>
-    <t>20084821</t>
-  </si>
-  <si>
-    <t>FORTE MNTHL BKS 20'S</t>
-  </si>
-  <si>
-    <t>20132549</t>
-  </si>
-  <si>
-    <t>FORTE MANGO BKS 20'S</t>
-  </si>
-  <si>
-    <t>10014528</t>
-  </si>
-  <si>
-    <t>DJARUM BLACK FILTR16</t>
-  </si>
-  <si>
-    <t>10035030</t>
-  </si>
-  <si>
-    <t>DJRM BLACK CPCINO 16</t>
-  </si>
-  <si>
-    <t>20131992</t>
-  </si>
-  <si>
-    <t>DJARUM MILD F.COLA16</t>
-  </si>
-  <si>
-    <t>20046279</t>
-  </si>
-  <si>
-    <t>DJARUM SPR MILD 20'S</t>
-  </si>
-  <si>
-    <t>20075616</t>
-  </si>
-  <si>
-    <t>DJARUM MILD BLCK 12S</t>
-  </si>
-  <si>
-    <t>10010087</t>
-  </si>
-  <si>
-    <t>MR.BROWN COFFEE 12'S</t>
-  </si>
-  <si>
-    <t>20136123</t>
-  </si>
-  <si>
-    <t>DJARUM ESPRSO GLD12S</t>
-  </si>
-  <si>
-    <t>20132548</t>
-  </si>
-  <si>
-    <t>DJARUM ESPRESSO 12'S</t>
-  </si>
-  <si>
-    <t>20140378</t>
-  </si>
-  <si>
-    <t>DJARUM SUPER WRAP12S</t>
-  </si>
-  <si>
-    <t>20139142</t>
-  </si>
-  <si>
-    <t>DJRM CGRILLOS FC 12S</t>
-  </si>
-  <si>
-    <t>10010081</t>
-  </si>
-  <si>
-    <t>DJARUM SUPER FILTR12</t>
-  </si>
-  <si>
-    <t>10010082</t>
-  </si>
-  <si>
-    <t>DJARUM SUPER FILTR16</t>
-  </si>
-  <si>
-    <t>20126488</t>
-  </si>
-  <si>
-    <t>DJARUM KING FLTER 12</t>
-  </si>
-  <si>
-    <t>20075632</t>
-  </si>
-  <si>
-    <t>LA BOLD BKS 12'S</t>
-  </si>
-  <si>
-    <t>20062125</t>
-  </si>
-  <si>
-    <t>LA BOLD BKS 20'S</t>
-  </si>
-  <si>
-    <t>20134688</t>
-  </si>
-  <si>
-    <t>LA BOLD BKS NEW 16'S</t>
-  </si>
-  <si>
-    <t>20124037</t>
-  </si>
-  <si>
-    <t>LA ICE FL PR/BST 16S</t>
-  </si>
-  <si>
-    <t>20135993</t>
-  </si>
-  <si>
-    <t>LA ICE MANGO BST 16S</t>
-  </si>
-  <si>
-    <t>20048746</t>
-  </si>
-  <si>
-    <t>LA ICE 16'S BKS</t>
-  </si>
-  <si>
-    <t>10010084</t>
-  </si>
-  <si>
-    <t>LA FILTER LIGHT 16'S</t>
-  </si>
-  <si>
     <t>20137797</t>
   </si>
   <si>
@@ -1172,6 +1172,12 @@
   </si>
   <si>
     <t>JUARA  JAMBU12S</t>
+  </si>
+  <si>
+    <t>20141660</t>
+  </si>
+  <si>
+    <t>JUARA KRT PISANG 12S</t>
   </si>
   <si>
     <t>20085760</t>
@@ -1708,7 +1714,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F208"/>
+  <dimension ref="A1:F209"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1915,15 +1921,15 @@
         <v>29</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -1932,7 +1938,7 @@
         <v>4</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>5</v>
@@ -1940,10 +1946,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -1952,10 +1958,10 @@
         <v>4</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -2009,10 +2015,10 @@
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>45</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>5</v>
@@ -2020,19 +2026,19 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>5</v>
@@ -2040,10 +2046,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -2052,18 +2058,18 @@
         <v>8</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -2072,18 +2078,18 @@
         <v>8</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -2092,18 +2098,18 @@
         <v>8</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -2112,18 +2118,18 @@
         <v>8</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>55</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -2132,18 +2138,18 @@
         <v>8</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>55</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -2152,7 +2158,7 @@
         <v>8</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>5</v>
@@ -2160,10 +2166,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -2172,7 +2178,7 @@
         <v>8</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>5</v>
@@ -2180,10 +2186,10 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -2192,7 +2198,7 @@
         <v>8</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>5</v>
@@ -2200,10 +2206,10 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -2212,7 +2218,7 @@
         <v>8</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>5</v>
@@ -2220,10 +2226,10 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
@@ -2232,7 +2238,7 @@
         <v>8</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>5</v>
@@ -2240,10 +2246,10 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
@@ -2252,18 +2258,18 @@
         <v>8</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>73</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
@@ -2272,10 +2278,10 @@
         <v>8</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -2289,41 +2295,41 @@
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>76</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="F30" s="1" t="s">
-        <v>76</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
@@ -2332,18 +2338,18 @@
         <v>11</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>82</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
@@ -2352,7 +2358,7 @@
         <v>11</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>5</v>
@@ -2360,10 +2366,10 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>84</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
@@ -2372,18 +2378,18 @@
         <v>11</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>76</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>86</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
@@ -2392,18 +2398,18 @@
         <v>11</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>88</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
@@ -2412,7 +2418,7 @@
         <v>11</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>5</v>
@@ -2420,10 +2426,10 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>90</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
@@ -2432,7 +2438,7 @@
         <v>11</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>5</v>
@@ -2440,10 +2446,10 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>92</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
@@ -2452,18 +2458,18 @@
         <v>11</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>94</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
@@ -2472,7 +2478,7 @@
         <v>11</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>5</v>
@@ -2480,10 +2486,10 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>96</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
@@ -2492,7 +2498,7 @@
         <v>11</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>5</v>
@@ -2500,10 +2506,10 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>98</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
@@ -2512,67 +2518,67 @@
         <v>11</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B41" s="1" t="s">
-        <v>100</v>
-      </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B42" s="1" t="s">
-        <v>102</v>
-      </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>76</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B43" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E43" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>5</v>
@@ -2580,19 +2586,19 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>106</v>
-      </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>5</v>
@@ -2600,10 +2606,10 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>108</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -2612,18 +2618,18 @@
         <v>14</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>76</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>110</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
@@ -2632,7 +2638,7 @@
         <v>14</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>5</v>
@@ -2640,10 +2646,10 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>112</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
@@ -2652,7 +2658,7 @@
         <v>14</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>5</v>
@@ -2660,10 +2666,10 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>114</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
@@ -2672,18 +2678,18 @@
         <v>14</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>116</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
@@ -2692,7 +2698,7 @@
         <v>14</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>5</v>
@@ -2700,10 +2706,10 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>118</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
@@ -2712,7 +2718,7 @@
         <v>14</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>5</v>
@@ -2720,10 +2726,10 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>120</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
@@ -2732,7 +2738,7 @@
         <v>14</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>5</v>
@@ -2740,10 +2746,10 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>122</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
@@ -2752,7 +2758,7 @@
         <v>14</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -2760,10 +2766,10 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>124</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
@@ -2772,18 +2778,18 @@
         <v>14</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>125</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>126</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
@@ -2792,27 +2798,27 @@
         <v>14</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>76</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>128</v>
-      </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>5</v>
@@ -2820,39 +2826,39 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B56" s="1" t="s">
-        <v>130</v>
-      </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B57" s="1" t="s">
-        <v>132</v>
-      </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>5</v>
@@ -2860,19 +2866,19 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B58" s="1" t="s">
-        <v>134</v>
-      </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E58" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>45</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -2880,10 +2886,10 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>135</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>136</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
@@ -2892,7 +2898,7 @@
         <v>17</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>5</v>
@@ -2900,10 +2906,10 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>138</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
@@ -2912,18 +2918,18 @@
         <v>17</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>76</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>139</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>140</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
@@ -2932,7 +2938,7 @@
         <v>17</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>5</v>
@@ -2940,10 +2946,10 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>141</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>142</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
@@ -2952,7 +2958,7 @@
         <v>17</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>5</v>
@@ -2960,10 +2966,10 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>143</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>144</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
@@ -2972,7 +2978,7 @@
         <v>17</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -2980,10 +2986,10 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B64" s="1" t="s">
         <v>145</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>146</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
@@ -2992,18 +2998,18 @@
         <v>17</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>147</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>148</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
@@ -3012,7 +3018,7 @@
         <v>17</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>5</v>
@@ -3020,10 +3026,10 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>150</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
@@ -3032,7 +3038,7 @@
         <v>17</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>5</v>
@@ -3040,10 +3046,10 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>151</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>152</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
@@ -3052,7 +3058,7 @@
         <v>17</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>5</v>
@@ -3060,10 +3066,10 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B68" s="1" t="s">
         <v>153</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>154</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
@@ -3072,10 +3078,10 @@
         <v>17</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>35</v>
+        <v>154</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -3089,10 +3095,10 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>5</v>
@@ -3109,10 +3115,10 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>5</v>
@@ -3132,7 +3138,7 @@
         <v>20</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>5</v>
@@ -3152,7 +3158,7 @@
         <v>20</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>5</v>
@@ -3172,7 +3178,7 @@
         <v>20</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>5</v>
@@ -3192,7 +3198,7 @@
         <v>20</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>5</v>
@@ -3212,7 +3218,7 @@
         <v>20</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>5</v>
@@ -3232,7 +3238,7 @@
         <v>20</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>5</v>
@@ -3249,10 +3255,10 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -3269,10 +3275,10 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -3292,7 +3298,7 @@
         <v>23</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -3312,7 +3318,7 @@
         <v>23</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3332,7 +3338,7 @@
         <v>23</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -3352,7 +3358,7 @@
         <v>23</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -3372,7 +3378,7 @@
         <v>23</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -3392,7 +3398,7 @@
         <v>23</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -3412,7 +3418,7 @@
         <v>23</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -3432,7 +3438,7 @@
         <v>23</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -3452,7 +3458,7 @@
         <v>23</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>5</v>
@@ -3472,7 +3478,7 @@
         <v>23</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>5</v>
@@ -3492,7 +3498,7 @@
         <v>23</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3509,10 +3515,10 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3529,10 +3535,10 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>5</v>
@@ -3552,7 +3558,7 @@
         <v>26</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3572,7 +3578,7 @@
         <v>26</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -3592,7 +3598,7 @@
         <v>26</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3612,7 +3618,7 @@
         <v>26</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3632,10 +3638,10 @@
         <v>26</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3652,7 +3658,7 @@
         <v>26</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3672,10 +3678,10 @@
         <v>26</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>55</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3692,7 +3698,7 @@
         <v>26</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3709,10 +3715,10 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3729,10 +3735,10 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3752,7 +3758,7 @@
         <v>29</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3772,7 +3778,7 @@
         <v>29</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3792,7 +3798,7 @@
         <v>29</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3812,7 +3818,7 @@
         <v>29</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3832,7 +3838,7 @@
         <v>29</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3852,10 +3858,10 @@
         <v>29</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -3872,7 +3878,7 @@
         <v>29</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -3889,7 +3895,7 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>4</v>
@@ -3909,7 +3915,7 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>4</v>
@@ -3929,7 +3935,7 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>4</v>
@@ -3949,7 +3955,7 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>4</v>
@@ -3969,7 +3975,7 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>4</v>
@@ -3989,7 +3995,7 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>8</v>
@@ -4009,7 +4015,7 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>8</v>
@@ -4029,13 +4035,13 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -4049,7 +4055,7 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>8</v>
@@ -4069,7 +4075,7 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>11</v>
@@ -4089,7 +4095,7 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>11</v>
@@ -4109,7 +4115,7 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>11</v>
@@ -4129,13 +4135,13 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -4149,7 +4155,7 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>14</v>
@@ -4169,7 +4175,7 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>14</v>
@@ -4189,7 +4195,7 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>14</v>
@@ -4209,7 +4215,7 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>17</v>
@@ -4229,7 +4235,7 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>17</v>
@@ -4249,7 +4255,7 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E127" s="1" t="s">
         <v>17</v>
@@ -4269,7 +4275,7 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>17</v>
@@ -4289,13 +4295,13 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E129" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -4309,7 +4315,7 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E130" s="1" t="s">
         <v>20</v>
@@ -4329,7 +4335,7 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>20</v>
@@ -4349,7 +4355,7 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>20</v>
@@ -4369,13 +4375,13 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>20</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4389,13 +4395,13 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E134" s="1" t="s">
         <v>20</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -4409,13 +4415,13 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>20</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4429,7 +4435,7 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>20</v>
@@ -4449,7 +4455,7 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>20</v>
@@ -4469,7 +4475,7 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E138" s="1" t="s">
         <v>20</v>
@@ -4489,7 +4495,7 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>20</v>
@@ -4509,7 +4515,7 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>20</v>
@@ -4529,7 +4535,7 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E141" s="1" t="s">
         <v>20</v>
@@ -4549,7 +4555,7 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E142" s="1" t="s">
         <v>20</v>
@@ -4569,7 +4575,7 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E143" s="1" t="s">
         <v>20</v>
@@ -4589,13 +4595,13 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -4609,13 +4615,13 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E145" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -4629,13 +4635,13 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -4649,13 +4655,13 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -4669,7 +4675,7 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>23</v>
@@ -4689,7 +4695,7 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E149" s="1" t="s">
         <v>23</v>
@@ -4709,7 +4715,7 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>23</v>
@@ -4729,7 +4735,7 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>23</v>
@@ -4749,7 +4755,7 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E152" s="1" t="s">
         <v>23</v>
@@ -4769,7 +4775,7 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E153" s="1" t="s">
         <v>26</v>
@@ -4789,7 +4795,7 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E154" s="1" t="s">
         <v>4</v>
@@ -4809,7 +4815,7 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>8</v>
@@ -4829,7 +4835,7 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>11</v>
@@ -4849,7 +4855,7 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E157" s="1" t="s">
         <v>14</v>
@@ -4869,7 +4875,7 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>17</v>
@@ -4889,7 +4895,7 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>20</v>
@@ -4909,7 +4915,7 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>23</v>
@@ -4929,7 +4935,7 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>26</v>
@@ -4949,7 +4955,7 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>29</v>
@@ -4969,10 +4975,10 @@
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>5</v>
@@ -4989,10 +4995,10 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>5</v>
@@ -5009,13 +5015,13 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>39</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -5029,7 +5035,7 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>42</v>
@@ -5232,7 +5238,7 @@
         <v>39</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>5</v>
@@ -5252,7 +5258,7 @@
         <v>39</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>5</v>
@@ -5412,10 +5418,10 @@
         <v>42</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -5432,7 +5438,7 @@
         <v>42</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>5</v>
@@ -5452,7 +5458,7 @@
         <v>42</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>5</v>
@@ -5472,7 +5478,7 @@
         <v>42</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>5</v>
@@ -5492,7 +5498,7 @@
         <v>42</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>5</v>
@@ -5512,7 +5518,7 @@
         <v>42</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>5</v>
@@ -5532,7 +5538,7 @@
         <v>42</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>5</v>
@@ -5552,10 +5558,10 @@
         <v>42</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -5572,10 +5578,10 @@
         <v>42</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
@@ -5589,13 +5595,13 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>4</v>
+        <v>154</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>76</v>
+        <v>30</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
@@ -5609,13 +5615,13 @@
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
@@ -5629,13 +5635,13 @@
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -5649,13 +5655,13 @@
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -5669,13 +5675,13 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -5689,13 +5695,13 @@
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
@@ -5709,13 +5715,13 @@
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -5729,13 +5735,13 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
@@ -5749,13 +5755,13 @@
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>48</v>
+        <v>154</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
@@ -5769,13 +5775,13 @@
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>48</v>
+        <v>154</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
@@ -5789,13 +5795,13 @@
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>48</v>
+        <v>154</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -5809,13 +5815,13 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>48</v>
+        <v>154</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
@@ -5829,13 +5835,13 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>48</v>
+        <v>154</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
@@ -5849,13 +5855,13 @@
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>48</v>
+        <v>154</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
@@ -5869,13 +5875,33 @@
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>48</v>
+        <v>154</v>
       </c>
       <c r="E208" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F208" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A209" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B209" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D209" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E209" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F208" s="1" t="s">
-        <v>76</v>
+      <c r="F209" s="1" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
